--- a/Member list with dates and officers.xlsx
+++ b/Member list with dates and officers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidphilllips/Documents/working_files/personal/Cooperdale Church of the Nazarene/Board Meeting Agenda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nphil\Documents\Code\cooperDale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89545E6-67BF-CF49-9DFB-833E9E39FA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BA76D1-4C36-44A8-947F-4A73B8AA6CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="500" windowWidth="25440" windowHeight="14900" xr2:uid="{3A1112AB-5BED-A64A-BFD0-B8FBCAEBCCAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3A1112AB-5BED-A64A-BFD0-B8FBCAEBCCAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="94">
-  <si>
-    <t>Cooperdale Nazarene Membership</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -746,115 +743,128 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" customWidth="1"/>
-    <col min="3" max="4" width="10.83203125" style="1"/>
-    <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
-    <col min="6" max="11" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" customWidth="1"/>
+    <col min="3" max="4" width="10.875" style="1"/>
+    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
+    <col min="6" max="11" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2019</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2019</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A48" si="0">A3+1</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I3" s="1">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <f t="shared" ref="A5:A49" si="0">A4+1</f>
-        <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>68</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2019</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>69</v>
@@ -863,34 +873,34 @@
         <v>2019</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1">
         <v>2019</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>67</v>
@@ -899,139 +909,136 @@
         <v>2019</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2">
+        <v>44696</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
       <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="2">
-        <v>44696</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="C16" s="7">
+        <v>44562</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
@@ -1040,73 +1047,73 @@
         <v>44562</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="7">
-        <v>44562</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
       <c r="C20" s="1">
         <v>2019</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1">
         <v>2019</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>73</v>
@@ -1115,88 +1122,88 @@
         <v>2019</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C23" s="1">
         <v>2019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="7">
+        <v>44696</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
       </c>
       <c r="C25" s="7">
-        <v>44696</v>
-      </c>
-      <c r="F25" s="1" t="s">
+        <v>44759</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="7">
-        <v>44759</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="C27" s="7">
+        <v>44197</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
         <v>71</v>
@@ -1205,88 +1212,88 @@
         <v>44197</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="7">
+        <v>45354</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="7">
-        <v>44197</v>
-      </c>
-      <c r="F29" s="1" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="7">
+        <v>45053</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="7">
+        <v>45249</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="7">
-        <v>45354</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="7">
-        <v>45053</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="7">
-        <v>45249</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>65</v>
@@ -1295,28 +1302,28 @@
         <v>2019</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2021</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>81</v>
@@ -1325,43 +1332,43 @@
         <v>2021</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2019</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="8">
-        <v>2019</v>
+        <v>58</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2015</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
@@ -1370,58 +1377,58 @@
         <v>2015</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C40" s="1">
         <v>2015</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="1">
-        <v>2015</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C42" s="1">
-        <v>2020</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2019</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
         <v>61</v>
@@ -1430,43 +1437,43 @@
         <v>2019</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="1">
-        <v>2019</v>
+        <v>78</v>
+      </c>
+      <c r="C44" s="7">
+        <v>45053</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C45" s="7">
-        <v>45053</v>
+        <v>45536</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
         <v>92</v>
@@ -1475,41 +1482,26 @@
         <v>45536</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="7">
-        <v>45536</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1">
-        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K45">
-    <sortCondition ref="I3:I45"/>
-    <sortCondition ref="G3:G45"/>
-    <sortCondition ref="B3:B45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K44">
+    <sortCondition ref="I2:I44"/>
+    <sortCondition ref="G2:G44"/>
+    <sortCondition ref="B2:B44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="89" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="8"/>
@@ -1519,55 +1511,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDC3CF4-A251-CF43-B573-C9233CD4C9E9}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" t="s">
-        <v>91</v>
-      </c>
       <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
         <v>90</v>
       </c>
-      <c r="H1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>2022</v>
@@ -1597,191 +1589,191 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="D6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="I11" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="I14" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="13">
         <f>9/28</f>
         <v>0.32142857142857145</v>
